--- a/data/externalStats/File1/RPT_RPT9118491557157QP_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT9118491557157QP_externalStats.xlsx
@@ -2104,7 +2104,7 @@
         <v>28321869.63325635</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>37842.22928475847</v>
+        <v>37842.22928475848</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -3911,7 +3911,7 @@
         <v>3332.621486685727</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>833.0894434723068</v>
+        <v>833.0894434723069</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
         <v>6634.756448314753</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>3383.039931822101</v>
+        <v>3383.039931822102</v>
       </c>
       <c r="X53" s="128" t="n">
         <v>816.5124351978794</v>
@@ -4067,10 +4067,10 @@
         <v>20917</v>
       </c>
       <c r="J55" s="130" t="n">
-        <v>21080.77407711741</v>
+        <v>21080.77407711742</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>951.1333611046695</v>
+        <v>951.1333611046697</v>
       </c>
       <c r="L55" s="131" t="n">
         <v>61.23579467953606</v>
@@ -4085,7 +4085,7 @@
         <v>21674.50215177691</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>991.3204392584844</v>
+        <v>991.3204392584845</v>
       </c>
       <c r="R55" s="131" t="n">
         <v>63.05746500463982</v>
@@ -4103,7 +4103,7 @@
         <v>1023.671300995067</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>64.74488708336855</v>
+        <v>64.74488708336854</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -4123,7 +4123,7 @@
         <v>1652160.935343546</v>
       </c>
       <c r="AH55" s="56" t="n">
-        <v>4793.408093083508</v>
+        <v>4793.408093083509</v>
       </c>
     </row>
     <row r="56">
@@ -4229,19 +4229,19 @@
         <v>15485</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>6746.935336864784</v>
+        <v>6746.935336864786</v>
       </c>
       <c r="K57" s="131" t="n">
-        <v>1274.799268573767</v>
+        <v>1274.799268573766</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>468.5634983662505</v>
+        <v>468.5634983662507</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>10.76678424032055</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8501.064888045123</v>
+        <v>8501.064888045124</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>6890.578425007416</v>
@@ -4262,10 +4262,10 @@
         <v>7235.557701200762</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>1311.171925375474</v>
+        <v>1311.171925375475</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>478.4300451277439</v>
+        <v>478.4300451277438</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>11.62034978511225</v>
@@ -4400,10 +4400,10 @@
         <v>0</v>
       </c>
       <c r="M59" s="131" t="n">
-        <v>480.5890560334112</v>
+        <v>480.5890560334113</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>480.5890560334112</v>
+        <v>480.5890560334113</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>0</v>
@@ -4415,10 +4415,10 @@
         <v>0</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>503.5137707099607</v>
+        <v>503.5137707099605</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>503.5137707099607</v>
+        <v>503.5137707099605</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>0</v>
@@ -4553,13 +4553,13 @@
         <v>27180</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>2379.655877793457</v>
+        <v>2379.655877793458</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>603.0630369926311</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>225.5148079810755</v>
+        <v>225.5148079810754</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>22.80962481997878</v>
@@ -4580,22 +4580,22 @@
         <v>23.34018512080814</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>3384.873682270296</v>
+        <v>3384.873682270295</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>2591.177460907065</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>671.6768219502637</v>
+        <v>671.6768219502641</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>247.0930019032081</v>
+        <v>247.093001903208</v>
       </c>
       <c r="Y61" s="131" t="n">
         <v>24.13833300166812</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>3534.085617762205</v>
+        <v>3534.085617762206</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -4721,7 +4721,7 @@
         <v>953.9922867363875</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>320.5947597749855</v>
+        <v>320.5947597749851</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>15681.27426545956</v>
@@ -4748,13 +4748,13 @@
         <v>6662.484569964501</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1286.390850729029</v>
+        <v>1286.390850729027</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>409.1369923701982</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>19269.94930292226</v>
+        <v>19269.94930292225</v>
       </c>
       <c r="Z63" s="132" t="n">
         <v>27627.96171598598</v>
@@ -4835,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>19197.57468923769</v>
+        <v>19197.57468923768</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>19197.57468923769</v>
+        <v>19197.57468923768</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -5051,16 +5051,16 @@
         <v>2662.427529471637</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>881.2611282689422</v>
+        <v>881.2611282689423</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>273.3095391711202</v>
+        <v>273.3095391711204</v>
       </c>
       <c r="N67" s="141" t="n">
         <v>14879.94587588111</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>8502.990848158244</v>
+        <v>8502.990848158246</v>
       </c>
       <c r="Q67" s="140" t="n">
         <v>1843.726306856785</v>
@@ -5069,7 +5069,7 @@
         <v>736.7815134418789</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>298.1160255987033</v>
+        <v>298.1160255987032</v>
       </c>
       <c r="T67" s="141" t="n">
         <v>11381.61469405561</v>
@@ -5081,7 +5081,7 @@
         <v>1343.153224553199</v>
       </c>
       <c r="X67" s="140" t="n">
-        <v>654.8099860584188</v>
+        <v>654.8099860584185</v>
       </c>
       <c r="Y67" s="140" t="n">
         <v>377.8047822787307</v>
@@ -5138,13 +5138,13 @@
         <v>16468.74926972439</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>97613.00453511404</v>
+        <v>97613.00453511406</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>51981.41011538231</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>9188.302808746161</v>
+        <v>9188.302808746163</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>2683.316339065291</v>
@@ -5153,7 +5153,7 @@
         <v>18174.27692598257</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>99296.33164210043</v>
+        <v>99296.33164210041</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>52470.61975794812</v>
@@ -5339,16 +5339,16 @@
         <v>6151.28413401941</v>
       </c>
       <c r="K71" s="128" t="n">
-        <v>1095.842816267823</v>
+        <v>1095.842816267824</v>
       </c>
       <c r="L71" s="128" t="n">
-        <v>353.777097941825</v>
+        <v>353.7770979418252</v>
       </c>
       <c r="M71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>7600.904048229057</v>
+        <v>7600.904048229059</v>
       </c>
       <c r="P71" s="127" t="n">
         <v>6287.041516213972</v>
@@ -5363,7 +5363,7 @@
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7785.634170715169</v>
+        <v>7785.634170715168</v>
       </c>
       <c r="V71" s="127" t="n">
         <v>6391.592060490513</v>
@@ -5372,7 +5372,7 @@
         <v>1169.252393113846</v>
       </c>
       <c r="X71" s="128" t="n">
-        <v>374.0976984907914</v>
+        <v>374.0976984907912</v>
       </c>
       <c r="Y71" s="128" t="n">
         <v>0</v>
@@ -5613,19 +5613,19 @@
         <v>493.3573332324296</v>
       </c>
       <c r="M75" s="131" t="n">
-        <v>15.02795186804108</v>
+        <v>15.02795186804107</v>
       </c>
       <c r="N75" s="132" t="n">
         <v>10741.10803940695</v>
       </c>
       <c r="P75" s="130" t="n">
-        <v>8778.963966004183</v>
+        <v>8778.963966004181</v>
       </c>
       <c r="Q75" s="131" t="n">
-        <v>2736.176993753839</v>
+        <v>2736.176993753838</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>571.1780149937247</v>
+        <v>571.1780149937246</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>15.32446357326684</v>
@@ -5640,7 +5640,7 @@
         <v>3058.215331153287</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>634.9094649431017</v>
+        <v>634.9094649431015</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>15.63577962805127</v>
@@ -5887,10 +5887,10 @@
         <v>627.1079570083781</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>740.6580467347986</v>
+        <v>740.6580467347984</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>50.76288255445774</v>
+        <v>50.76288255445775</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>12.72211946021124</v>
@@ -5899,22 +5899,22 @@
         <v>0</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>804.1430487494677</v>
+        <v>804.1430487494674</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>895.7715527680019</v>
+        <v>895.7715527680018</v>
       </c>
       <c r="W79" s="131" t="n">
-        <v>77.24308810925419</v>
+        <v>77.2430881092542</v>
       </c>
       <c r="X79" s="131" t="n">
-        <v>20.49057430502566</v>
+        <v>20.49057430502565</v>
       </c>
       <c r="Y79" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>993.5052151822819</v>
+        <v>993.5052151822817</v>
       </c>
     </row>
     <row r="80">
@@ -6015,10 +6015,10 @@
         <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>1302.605115396208</v>
+        <v>1302.605115396207</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>1302.605115396208</v>
+        <v>1302.605115396207</v>
       </c>
       <c r="P81" s="130" t="n">
         <v>0</v>
@@ -6042,13 +6042,13 @@
         <v>0</v>
       </c>
       <c r="X81" s="131" t="n">
-        <v>7.275957614183426e-12</v>
+        <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
         <v>1640.848956006674</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>1640.848956006681</v>
+        <v>1640.848956006674</v>
       </c>
     </row>
     <row r="82">
@@ -6082,10 +6082,10 @@
         <v>0</v>
       </c>
       <c r="M82" s="134" t="n">
-        <v>1302.605115396208</v>
+        <v>1302.605115396207</v>
       </c>
       <c r="N82" s="135" t="n">
-        <v>1302.605115396208</v>
+        <v>1302.605115396207</v>
       </c>
       <c r="P82" s="133" t="n">
         <v>0</v>
@@ -6317,7 +6317,7 @@
         <v>57598.1825207315</v>
       </c>
       <c r="Y85" s="140" t="n">
-        <v>267.2782745528123</v>
+        <v>267.2782745528122</v>
       </c>
       <c r="Z85" s="141" t="n">
         <v>1420894.459244691</v>
@@ -6381,7 +6381,7 @@
         <v>253995.9035744286</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>58627.68025847042</v>
+        <v>58627.68025847041</v>
       </c>
       <c r="Y86" s="143" t="n">
         <v>1977.290320302254</v>
@@ -6568,13 +6568,13 @@
         <v>0</v>
       </c>
       <c r="T89" s="129" t="n">
-        <v>18615.09985330715</v>
+        <v>18615.09985330716</v>
       </c>
       <c r="V89" s="127" t="n">
         <v>13026.34850880527</v>
       </c>
       <c r="W89" s="128" t="n">
-        <v>4552.292324935946</v>
+        <v>4552.292324935947</v>
       </c>
       <c r="X89" s="128" t="n">
         <v>1190.610133688671</v>
@@ -6675,10 +6675,10 @@
         <v>20917</v>
       </c>
       <c r="J91" s="130" t="n">
-        <v>21080.77407711741</v>
+        <v>21080.77407711742</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>951.1333611046695</v>
+        <v>951.1333611046697</v>
       </c>
       <c r="L91" s="131" t="n">
         <v>61.23579467953606</v>
@@ -6693,7 +6693,7 @@
         <v>21674.50215177691</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>991.3204392584844</v>
+        <v>991.3204392584845</v>
       </c>
       <c r="R91" s="131" t="n">
         <v>63.05746500463982</v>
@@ -6711,7 +6711,7 @@
         <v>1023.671300995067</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>64.74488708336855</v>
+        <v>64.74488708336854</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -6815,7 +6815,7 @@
         <v>3640.25820473868</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>961.92083159868</v>
+        <v>961.9208315986803</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>25.79473610836162</v>
@@ -6842,10 +6842,10 @@
         <v>16813.67286703419</v>
       </c>
       <c r="W93" s="131" t="n">
-        <v>4369.387256528761</v>
+        <v>4369.387256528762</v>
       </c>
       <c r="X93" s="131" t="n">
-        <v>1113.339510070846</v>
+        <v>1113.339510070845</v>
       </c>
       <c r="Y93" s="131" t="n">
         <v>27.25612941316352</v>
@@ -6952,10 +6952,10 @@
         <v>0</v>
       </c>
       <c r="M95" s="131" t="n">
-        <v>497.2321863036293</v>
+        <v>497.2321863036294</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>497.2321863036293</v>
+        <v>497.2321863036294</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>0</v>
@@ -6967,10 +6967,10 @@
         <v>0</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>531.6202297178928</v>
+        <v>531.6202297178926</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>531.6202297178928</v>
+        <v>531.6202297178926</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -7089,10 +7089,10 @@
         <v>22.80962481997878</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>3858.15130459552</v>
+        <v>3858.151304595521</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>3227.374752548553</v>
+        <v>3227.374752548552</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>689.3815929441711</v>
@@ -7104,22 +7104,22 @@
         <v>23.34018512080814</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>4189.016731019764</v>
+        <v>4189.016731019763</v>
       </c>
       <c r="V97" s="130" t="n">
         <v>3486.949013675067</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>748.9199100595179</v>
+        <v>748.9199100595183</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>267.5835762082338</v>
+        <v>267.5835762082337</v>
       </c>
       <c r="Y97" s="131" t="n">
         <v>24.13833300166812</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>4527.590832944486</v>
+        <v>4527.590832944487</v>
       </c>
     </row>
     <row r="98">
@@ -7220,7 +7220,7 @@
         <v>320.594759774991</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>16983.87938085577</v>
+        <v>16983.87938085576</v>
       </c>
       <c r="N99" s="132" t="n">
         <v>23292.7240438382</v>
@@ -7247,13 +7247,13 @@
         <v>1286.390850729047</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>409.1369923702005</v>
+        <v>409.1369923701932</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>20910.79825892893</v>
+        <v>20910.79825892892</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>29268.81067199288</v>
+        <v>29268.81067199286</v>
       </c>
     </row>
     <row r="100">
@@ -7302,10 +7302,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>18745.38435647285</v>
+        <v>18745.38435647284</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>18745.38435647285</v>
+        <v>18745.38435647284</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -7492,7 +7492,7 @@
         <v>57558.27330927954</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>413.0331345658013</v>
+        <v>413.0331345658014</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>1412872.598815222</v>
@@ -7507,7 +7507,7 @@
         <v>57902.36710961223</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>510.1782527668204</v>
+        <v>510.1782527668203</v>
       </c>
       <c r="T103" s="141" t="n">
         <v>1422103.938946906</v>
@@ -7586,10 +7586,10 @@
         <v>263015.0076298538</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>61298.40760621124</v>
+        <v>61298.40760621123</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>22180.09556515783</v>
+        <v>22180.09556515782</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>1550005.838670861</v>
@@ -8859,7 +8859,7 @@
         <v>4048908.72842178</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>13973.95203328434</v>
+        <v>13973.95203328433</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -9144,7 +9144,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>2230525.508568964</v>
+        <v>2230525.508568965</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>2223.40933748808</v>
@@ -9471,7 +9471,7 @@
         </is>
       </c>
       <c r="AN36" s="58" t="n">
-        <v>48.45562175271812</v>
+        <v>48.45562175271811</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickBot="1">
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>1038574.977780616</v>
+        <v>1038574.977780615</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>4601.051082730221</v>
@@ -9893,7 +9893,7 @@
         <v>968749.2903345296</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>68.96563643999998</v>
+        <v>68.96563644</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -10404,7 +10404,7 @@
         <v>6650022.839911909</v>
       </c>
       <c r="AH52" s="56" t="n">
-        <v>970.3522845416157</v>
+        <v>970.3522845416159</v>
       </c>
     </row>
     <row r="53">
@@ -10435,7 +10435,7 @@
         <v>3332.621486685727</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>833.0894434723068</v>
+        <v>833.0894434723069</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -10462,7 +10462,7 @@
         <v>6634.756448314753</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>3383.039931822101</v>
+        <v>3383.039931822102</v>
       </c>
       <c r="X53" s="128" t="n">
         <v>816.5124351978794</v>
@@ -10591,10 +10591,10 @@
         <v>20917</v>
       </c>
       <c r="J55" s="130" t="n">
-        <v>21080.77407711741</v>
+        <v>21080.77407711742</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>951.1333611046695</v>
+        <v>951.1333611046697</v>
       </c>
       <c r="L55" s="131" t="n">
         <v>61.23579467953606</v>
@@ -10609,7 +10609,7 @@
         <v>21674.50215177691</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>991.3204392584844</v>
+        <v>991.3204392584845</v>
       </c>
       <c r="R55" s="131" t="n">
         <v>63.05746500463982</v>
@@ -10627,7 +10627,7 @@
         <v>1023.671300995067</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>64.74488708336855</v>
+        <v>64.74488708336854</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -10753,19 +10753,19 @@
         <v>15485</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>6746.935336864784</v>
+        <v>6746.935336864786</v>
       </c>
       <c r="K57" s="131" t="n">
-        <v>1274.799268573767</v>
+        <v>1274.799268573766</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>468.5634983662505</v>
+        <v>468.5634983662507</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>10.76678424032055</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8501.064888045123</v>
+        <v>8501.064888045124</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>6890.578425007416</v>
@@ -10786,10 +10786,10 @@
         <v>7235.557701200762</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>1311.171925375474</v>
+        <v>1311.171925375475</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>478.4300451277439</v>
+        <v>478.4300451277438</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>11.62034978511225</v>
@@ -10887,7 +10887,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>1038574.977780616</v>
+        <v>1038574.977780615</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>4601.051082730221</v>
@@ -10924,10 +10924,10 @@
         <v>0</v>
       </c>
       <c r="M59" s="131" t="n">
-        <v>480.5890560334112</v>
+        <v>480.5890560334113</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>480.5890560334112</v>
+        <v>480.5890560334113</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>0</v>
@@ -10939,10 +10939,10 @@
         <v>0</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>503.5137707099607</v>
+        <v>503.5137707099605</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>503.5137707099607</v>
+        <v>503.5137707099605</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>0</v>
@@ -11077,13 +11077,13 @@
         <v>27180</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>2379.655877793457</v>
+        <v>2379.655877793458</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>603.0630369926311</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>225.5148079810755</v>
+        <v>225.5148079810754</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>22.80962481997878</v>
@@ -11104,22 +11104,22 @@
         <v>23.34018512080814</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>3384.873682270296</v>
+        <v>3384.873682270295</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>2591.177460907065</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>671.6768219502637</v>
+        <v>671.6768219502641</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>247.0930019032081</v>
+        <v>247.093001903208</v>
       </c>
       <c r="Y61" s="131" t="n">
         <v>24.13833300166812</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>3534.085617762205</v>
+        <v>3534.085617762206</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -11245,7 +11245,7 @@
         <v>953.9922867363875</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>320.5947597749855</v>
+        <v>320.5947597749851</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>15681.27426545956</v>
@@ -11272,13 +11272,13 @@
         <v>6662.484569964501</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1286.390850729029</v>
+        <v>1286.390850729027</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>409.1369923701982</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>19269.94930292226</v>
+        <v>19269.94930292225</v>
       </c>
       <c r="Z63" s="132" t="n">
         <v>27627.96171598598</v>
@@ -11359,10 +11359,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>19197.57468923769</v>
+        <v>19197.57468923768</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>19197.57468923769</v>
+        <v>19197.57468923768</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -11575,16 +11575,16 @@
         <v>2662.427529471637</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>881.2611282689422</v>
+        <v>881.2611282689423</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>273.3095391711202</v>
+        <v>273.3095391711204</v>
       </c>
       <c r="N67" s="141" t="n">
         <v>14879.94587588111</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>8502.990848158244</v>
+        <v>8502.990848158246</v>
       </c>
       <c r="Q67" s="140" t="n">
         <v>1843.726306856785</v>
@@ -11593,7 +11593,7 @@
         <v>736.7815134418789</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>298.1160255987033</v>
+        <v>298.1160255987032</v>
       </c>
       <c r="T67" s="141" t="n">
         <v>11381.61469405561</v>
@@ -11605,7 +11605,7 @@
         <v>1343.153224553199</v>
       </c>
       <c r="X67" s="140" t="n">
-        <v>654.8099860584188</v>
+        <v>654.8099860584185</v>
       </c>
       <c r="Y67" s="140" t="n">
         <v>377.8047822787307</v>
@@ -11662,13 +11662,13 @@
         <v>16468.74926972439</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>97613.00453511404</v>
+        <v>97613.00453511406</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>51981.41011538231</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>9188.302808746161</v>
+        <v>9188.302808746163</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>2683.316339065291</v>
@@ -11677,7 +11677,7 @@
         <v>18174.27692598257</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>99296.33164210043</v>
+        <v>99296.33164210041</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>52470.61975794812</v>
@@ -11863,16 +11863,16 @@
         <v>6151.28413401941</v>
       </c>
       <c r="K71" s="128" t="n">
-        <v>1095.842816267823</v>
+        <v>1095.842816267824</v>
       </c>
       <c r="L71" s="128" t="n">
-        <v>353.777097941825</v>
+        <v>353.7770979418252</v>
       </c>
       <c r="M71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>7600.904048229057</v>
+        <v>7600.904048229059</v>
       </c>
       <c r="P71" s="127" t="n">
         <v>6287.041516213972</v>
@@ -11887,7 +11887,7 @@
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7785.634170715169</v>
+        <v>7785.634170715168</v>
       </c>
       <c r="V71" s="127" t="n">
         <v>6391.592060490513</v>
@@ -11896,7 +11896,7 @@
         <v>1169.252393113846</v>
       </c>
       <c r="X71" s="128" t="n">
-        <v>374.0976984907914</v>
+        <v>374.0976984907912</v>
       </c>
       <c r="Y71" s="128" t="n">
         <v>0</v>
@@ -12137,19 +12137,19 @@
         <v>493.3573332324296</v>
       </c>
       <c r="M75" s="131" t="n">
-        <v>15.02795186804108</v>
+        <v>15.02795186804107</v>
       </c>
       <c r="N75" s="132" t="n">
         <v>10741.10803940695</v>
       </c>
       <c r="P75" s="130" t="n">
-        <v>8778.963966004183</v>
+        <v>8778.963966004181</v>
       </c>
       <c r="Q75" s="131" t="n">
-        <v>2736.176993753839</v>
+        <v>2736.176993753838</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>571.1780149937247</v>
+        <v>571.1780149937246</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>15.32446357326684</v>
@@ -12164,7 +12164,7 @@
         <v>3058.215331153287</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>634.9094649431017</v>
+        <v>634.9094649431015</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>15.63577962805127</v>
@@ -12411,10 +12411,10 @@
         <v>627.1079570083781</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>740.6580467347986</v>
+        <v>740.6580467347984</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>50.76288255445774</v>
+        <v>50.76288255445775</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>12.72211946021124</v>
@@ -12423,22 +12423,22 @@
         <v>0</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>804.1430487494677</v>
+        <v>804.1430487494674</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>895.7715527680019</v>
+        <v>895.7715527680018</v>
       </c>
       <c r="W79" s="131" t="n">
-        <v>77.24308810925419</v>
+        <v>77.2430881092542</v>
       </c>
       <c r="X79" s="131" t="n">
-        <v>20.49057430502566</v>
+        <v>20.49057430502565</v>
       </c>
       <c r="Y79" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>993.5052151822819</v>
+        <v>993.5052151822817</v>
       </c>
     </row>
     <row r="80">
@@ -12539,10 +12539,10 @@
         <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>1302.605115396208</v>
+        <v>1302.605115396207</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>1302.605115396208</v>
+        <v>1302.605115396207</v>
       </c>
       <c r="P81" s="130" t="n">
         <v>0</v>
@@ -12566,13 +12566,13 @@
         <v>0</v>
       </c>
       <c r="X81" s="131" t="n">
-        <v>7.275957614183426e-12</v>
+        <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
         <v>1640.848956006674</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>1640.848956006681</v>
+        <v>1640.848956006674</v>
       </c>
     </row>
     <row r="82">
@@ -12606,10 +12606,10 @@
         <v>0</v>
       </c>
       <c r="M82" s="134" t="n">
-        <v>1302.605115396208</v>
+        <v>1302.605115396207</v>
       </c>
       <c r="N82" s="135" t="n">
-        <v>1302.605115396208</v>
+        <v>1302.605115396207</v>
       </c>
       <c r="P82" s="133" t="n">
         <v>0</v>
@@ -12841,7 +12841,7 @@
         <v>57598.1825207315</v>
       </c>
       <c r="Y85" s="140" t="n">
-        <v>267.2782745528123</v>
+        <v>267.2782745528122</v>
       </c>
       <c r="Z85" s="141" t="n">
         <v>1420894.459244691</v>
@@ -12905,7 +12905,7 @@
         <v>253995.9035744286</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>58627.68025847042</v>
+        <v>58627.68025847041</v>
       </c>
       <c r="Y86" s="143" t="n">
         <v>1977.290320302254</v>
@@ -13092,13 +13092,13 @@
         <v>0</v>
       </c>
       <c r="T89" s="129" t="n">
-        <v>18615.09985330715</v>
+        <v>18615.09985330716</v>
       </c>
       <c r="V89" s="127" t="n">
         <v>13026.34850880527</v>
       </c>
       <c r="W89" s="128" t="n">
-        <v>4552.292324935946</v>
+        <v>4552.292324935947</v>
       </c>
       <c r="X89" s="128" t="n">
         <v>1190.610133688671</v>
@@ -13199,10 +13199,10 @@
         <v>20917</v>
       </c>
       <c r="J91" s="130" t="n">
-        <v>21080.77407711741</v>
+        <v>21080.77407711742</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>951.1333611046695</v>
+        <v>951.1333611046697</v>
       </c>
       <c r="L91" s="131" t="n">
         <v>61.23579467953606</v>
@@ -13217,7 +13217,7 @@
         <v>21674.50215177691</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>991.3204392584844</v>
+        <v>991.3204392584845</v>
       </c>
       <c r="R91" s="131" t="n">
         <v>63.05746500463982</v>
@@ -13235,7 +13235,7 @@
         <v>1023.671300995067</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>64.74488708336855</v>
+        <v>64.74488708336854</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -13339,7 +13339,7 @@
         <v>3640.25820473868</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>961.92083159868</v>
+        <v>961.9208315986803</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>25.79473610836162</v>
@@ -13366,10 +13366,10 @@
         <v>16813.67286703419</v>
       </c>
       <c r="W93" s="131" t="n">
-        <v>4369.387256528761</v>
+        <v>4369.387256528762</v>
       </c>
       <c r="X93" s="131" t="n">
-        <v>1113.339510070846</v>
+        <v>1113.339510070845</v>
       </c>
       <c r="Y93" s="131" t="n">
         <v>27.25612941316352</v>
@@ -13476,10 +13476,10 @@
         <v>0</v>
       </c>
       <c r="M95" s="131" t="n">
-        <v>497.2321863036293</v>
+        <v>497.2321863036294</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>497.2321863036293</v>
+        <v>497.2321863036294</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>0</v>
@@ -13491,10 +13491,10 @@
         <v>0</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>531.6202297178928</v>
+        <v>531.6202297178926</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>531.6202297178928</v>
+        <v>531.6202297178926</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -13613,10 +13613,10 @@
         <v>22.80962481997878</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>3858.15130459552</v>
+        <v>3858.151304595521</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>3227.374752548553</v>
+        <v>3227.374752548552</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>689.3815929441711</v>
@@ -13628,22 +13628,22 @@
         <v>23.34018512080814</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>4189.016731019764</v>
+        <v>4189.016731019763</v>
       </c>
       <c r="V97" s="130" t="n">
         <v>3486.949013675067</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>748.9199100595179</v>
+        <v>748.9199100595183</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>267.5835762082338</v>
+        <v>267.5835762082337</v>
       </c>
       <c r="Y97" s="131" t="n">
         <v>24.13833300166812</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>4527.590832944486</v>
+        <v>4527.590832944487</v>
       </c>
     </row>
     <row r="98">
@@ -13744,7 +13744,7 @@
         <v>320.594759774991</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>16983.87938085577</v>
+        <v>16983.87938085576</v>
       </c>
       <c r="N99" s="132" t="n">
         <v>23292.7240438382</v>
@@ -13771,13 +13771,13 @@
         <v>1286.390850729047</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>409.1369923702005</v>
+        <v>409.1369923701932</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>20910.79825892893</v>
+        <v>20910.79825892892</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>29268.81067199288</v>
+        <v>29268.81067199286</v>
       </c>
     </row>
     <row r="100">
@@ -13826,10 +13826,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>18745.38435647285</v>
+        <v>18745.38435647284</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>18745.38435647285</v>
+        <v>18745.38435647284</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -14016,7 +14016,7 @@
         <v>57558.27330927954</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>413.0331345658013</v>
+        <v>413.0331345658014</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>1412872.598815222</v>
@@ -14031,7 +14031,7 @@
         <v>57902.36710961223</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>510.1782527668204</v>
+        <v>510.1782527668203</v>
       </c>
       <c r="T103" s="141" t="n">
         <v>1422103.938946906</v>
@@ -14110,10 +14110,10 @@
         <v>263015.0076298538</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>61298.40760621124</v>
+        <v>61298.40760621123</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>22180.09556515783</v>
+        <v>22180.09556515782</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>1550005.838670861</v>
@@ -15152,7 +15152,7 @@
         <v>45235826.03390888</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>57217.44053621583</v>
+        <v>57217.44053621582</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -15168,7 +15168,7 @@
         </is>
       </c>
       <c r="AN25" s="48" t="n">
-        <v>647.687999404754</v>
+        <v>647.6879994047541</v>
       </c>
     </row>
     <row r="26">
@@ -15380,7 +15380,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>4659484.105036949</v>
+        <v>4659484.10503695</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>15724.71578175682</v>
@@ -15553,7 +15553,7 @@
         </is>
       </c>
       <c r="AN30" s="58" t="n">
-        <v>53.97399995039617</v>
+        <v>53.97399995039616</v>
       </c>
     </row>
     <row r="31">
@@ -15597,10 +15597,10 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>2921714.569335146</v>
+        <v>2921714.569335145</v>
       </c>
       <c r="AI31" s="56" t="n">
-        <v>5851.67611122417</v>
+        <v>5851.676111224169</v>
       </c>
       <c r="AK31" s="123" t="n">
         <v>7</v>
@@ -15748,7 +15748,7 @@
         <v>2569858.204487988</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>2396.74632943865</v>
+        <v>2396.746329438651</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -16491,7 +16491,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>884607.9620802103</v>
+        <v>884607.9620802102</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>1826.21205728125</v>
@@ -16745,7 +16745,7 @@
         <v>59315244.66163597</v>
       </c>
       <c r="AH49" s="46" t="n">
-        <v>74258.41862736084</v>
+        <v>74258.41862736085</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" thickBot="1">
@@ -16925,7 +16925,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>7732644.9983714</v>
+        <v>7732644.998371399</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>1020.301975533004</v>
@@ -16959,7 +16959,7 @@
         <v>3332.621486685727</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>833.0894434723068</v>
+        <v>833.0894434723069</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>6634.756448314753</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>3383.039931822101</v>
+        <v>3383.039931822102</v>
       </c>
       <c r="X53" s="128" t="n">
         <v>816.5124351978794</v>
@@ -17115,10 +17115,10 @@
         <v>20917</v>
       </c>
       <c r="J55" s="130" t="n">
-        <v>21080.77407711741</v>
+        <v>21080.77407711742</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>951.1333611046695</v>
+        <v>951.1333611046697</v>
       </c>
       <c r="L55" s="131" t="n">
         <v>61.23579467953606</v>
@@ -17133,7 +17133,7 @@
         <v>21674.50215177691</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>991.3204392584844</v>
+        <v>991.3204392584845</v>
       </c>
       <c r="R55" s="131" t="n">
         <v>63.05746500463982</v>
@@ -17151,7 +17151,7 @@
         <v>1023.671300995067</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>64.74488708336855</v>
+        <v>64.74488708336854</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -17277,19 +17277,19 @@
         <v>15485</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>6746.935336864784</v>
+        <v>6746.935336864786</v>
       </c>
       <c r="K57" s="131" t="n">
-        <v>1274.799268573767</v>
+        <v>1274.799268573766</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>468.5634983662505</v>
+        <v>468.5634983662507</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>10.76678424032055</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8501.064888045123</v>
+        <v>8501.064888045124</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>6890.578425007416</v>
@@ -17310,10 +17310,10 @@
         <v>7235.557701200762</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>1311.171925375474</v>
+        <v>1311.171925375475</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>478.4300451277439</v>
+        <v>478.4300451277438</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>11.62034978511225</v>
@@ -17448,10 +17448,10 @@
         <v>0</v>
       </c>
       <c r="M59" s="131" t="n">
-        <v>480.5890560334112</v>
+        <v>480.5890560334113</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>480.5890560334112</v>
+        <v>480.5890560334113</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>0</v>
@@ -17463,10 +17463,10 @@
         <v>0</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>503.5137707099607</v>
+        <v>503.5137707099605</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>503.5137707099607</v>
+        <v>503.5137707099605</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>0</v>
@@ -17601,13 +17601,13 @@
         <v>27180</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>2379.655877793457</v>
+        <v>2379.655877793458</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>603.0630369926311</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>225.5148079810755</v>
+        <v>225.5148079810754</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>22.80962481997878</v>
@@ -17628,22 +17628,22 @@
         <v>23.34018512080814</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>3384.873682270296</v>
+        <v>3384.873682270295</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>2591.177460907065</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>671.6768219502637</v>
+        <v>671.6768219502641</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>247.0930019032081</v>
+        <v>247.093001903208</v>
       </c>
       <c r="Y61" s="131" t="n">
         <v>24.13833300166812</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>3534.085617762205</v>
+        <v>3534.085617762206</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -17769,7 +17769,7 @@
         <v>953.9922867363875</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>320.5947597749855</v>
+        <v>320.5947597749851</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>15681.27426545956</v>
@@ -17796,13 +17796,13 @@
         <v>6662.484569964501</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1286.390850729029</v>
+        <v>1286.390850729027</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>409.1369923701982</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>19269.94930292226</v>
+        <v>19269.94930292225</v>
       </c>
       <c r="Z63" s="132" t="n">
         <v>27627.96171598598</v>
@@ -17883,10 +17883,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>19197.57468923769</v>
+        <v>19197.57468923768</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>19197.57468923769</v>
+        <v>19197.57468923768</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -18068,7 +18068,7 @@
         <v>300780.0250792875</v>
       </c>
       <c r="AH66" s="56" t="n">
-        <v>59.06647704988838</v>
+        <v>59.06647704988839</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" thickBot="1">
@@ -18099,16 +18099,16 @@
         <v>2662.427529471637</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>881.2611282689422</v>
+        <v>881.2611282689423</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>273.3095391711202</v>
+        <v>273.3095391711204</v>
       </c>
       <c r="N67" s="141" t="n">
         <v>14879.94587588111</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>8502.990848158244</v>
+        <v>8502.990848158246</v>
       </c>
       <c r="Q67" s="140" t="n">
         <v>1843.726306856785</v>
@@ -18117,7 +18117,7 @@
         <v>736.7815134418789</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>298.1160255987033</v>
+        <v>298.1160255987032</v>
       </c>
       <c r="T67" s="141" t="n">
         <v>11381.61469405561</v>
@@ -18129,7 +18129,7 @@
         <v>1343.153224553199</v>
       </c>
       <c r="X67" s="140" t="n">
-        <v>654.8099860584188</v>
+        <v>654.8099860584185</v>
       </c>
       <c r="Y67" s="140" t="n">
         <v>377.8047822787307</v>
@@ -18186,13 +18186,13 @@
         <v>16468.74926972439</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>97613.00453511404</v>
+        <v>97613.00453511406</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>51981.41011538231</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>9188.302808746161</v>
+        <v>9188.302808746163</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>2683.316339065291</v>
@@ -18201,7 +18201,7 @@
         <v>18174.27692598257</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>99296.33164210043</v>
+        <v>99296.33164210041</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>52470.61975794812</v>
@@ -18387,16 +18387,16 @@
         <v>6151.28413401941</v>
       </c>
       <c r="K71" s="128" t="n">
-        <v>1095.842816267823</v>
+        <v>1095.842816267824</v>
       </c>
       <c r="L71" s="128" t="n">
-        <v>353.777097941825</v>
+        <v>353.7770979418252</v>
       </c>
       <c r="M71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>7600.904048229057</v>
+        <v>7600.904048229059</v>
       </c>
       <c r="P71" s="127" t="n">
         <v>6287.041516213972</v>
@@ -18411,7 +18411,7 @@
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7785.634170715169</v>
+        <v>7785.634170715168</v>
       </c>
       <c r="V71" s="127" t="n">
         <v>6391.592060490513</v>
@@ -18420,7 +18420,7 @@
         <v>1169.252393113846</v>
       </c>
       <c r="X71" s="128" t="n">
-        <v>374.0976984907914</v>
+        <v>374.0976984907912</v>
       </c>
       <c r="Y71" s="128" t="n">
         <v>0</v>
@@ -18661,19 +18661,19 @@
         <v>493.3573332324296</v>
       </c>
       <c r="M75" s="131" t="n">
-        <v>15.02795186804108</v>
+        <v>15.02795186804107</v>
       </c>
       <c r="N75" s="132" t="n">
         <v>10741.10803940695</v>
       </c>
       <c r="P75" s="130" t="n">
-        <v>8778.963966004183</v>
+        <v>8778.963966004181</v>
       </c>
       <c r="Q75" s="131" t="n">
-        <v>2736.176993753839</v>
+        <v>2736.176993753838</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>571.1780149937247</v>
+        <v>571.1780149937246</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>15.32446357326684</v>
@@ -18688,7 +18688,7 @@
         <v>3058.215331153287</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>634.9094649431017</v>
+        <v>634.9094649431015</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>15.63577962805127</v>
@@ -18935,10 +18935,10 @@
         <v>627.1079570083781</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>740.6580467347986</v>
+        <v>740.6580467347984</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>50.76288255445774</v>
+        <v>50.76288255445775</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>12.72211946021124</v>
@@ -18947,22 +18947,22 @@
         <v>0</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>804.1430487494677</v>
+        <v>804.1430487494674</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>895.7715527680019</v>
+        <v>895.7715527680018</v>
       </c>
       <c r="W79" s="131" t="n">
-        <v>77.24308810925419</v>
+        <v>77.2430881092542</v>
       </c>
       <c r="X79" s="131" t="n">
-        <v>20.49057430502566</v>
+        <v>20.49057430502565</v>
       </c>
       <c r="Y79" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>993.5052151822819</v>
+        <v>993.5052151822817</v>
       </c>
     </row>
     <row r="80">
@@ -19063,10 +19063,10 @@
         <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>1302.605115396208</v>
+        <v>1302.605115396207</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>1302.605115396208</v>
+        <v>1302.605115396207</v>
       </c>
       <c r="P81" s="130" t="n">
         <v>0</v>
@@ -19090,13 +19090,13 @@
         <v>0</v>
       </c>
       <c r="X81" s="131" t="n">
-        <v>7.275957614183426e-12</v>
+        <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
         <v>1640.848956006674</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>1640.848956006681</v>
+        <v>1640.848956006674</v>
       </c>
     </row>
     <row r="82">
@@ -19130,10 +19130,10 @@
         <v>0</v>
       </c>
       <c r="M82" s="134" t="n">
-        <v>1302.605115396208</v>
+        <v>1302.605115396207</v>
       </c>
       <c r="N82" s="135" t="n">
-        <v>1302.605115396208</v>
+        <v>1302.605115396207</v>
       </c>
       <c r="P82" s="133" t="n">
         <v>0</v>
@@ -19365,7 +19365,7 @@
         <v>57598.1825207315</v>
       </c>
       <c r="Y85" s="140" t="n">
-        <v>267.2782745528123</v>
+        <v>267.2782745528122</v>
       </c>
       <c r="Z85" s="141" t="n">
         <v>1420894.459244691</v>
@@ -19429,7 +19429,7 @@
         <v>253995.9035744286</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>58627.68025847042</v>
+        <v>58627.68025847041</v>
       </c>
       <c r="Y86" s="143" t="n">
         <v>1977.290320302254</v>
@@ -19616,13 +19616,13 @@
         <v>0</v>
       </c>
       <c r="T89" s="129" t="n">
-        <v>18615.09985330715</v>
+        <v>18615.09985330716</v>
       </c>
       <c r="V89" s="127" t="n">
         <v>13026.34850880527</v>
       </c>
       <c r="W89" s="128" t="n">
-        <v>4552.292324935946</v>
+        <v>4552.292324935947</v>
       </c>
       <c r="X89" s="128" t="n">
         <v>1190.610133688671</v>
@@ -19723,10 +19723,10 @@
         <v>20917</v>
       </c>
       <c r="J91" s="130" t="n">
-        <v>21080.77407711741</v>
+        <v>21080.77407711742</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>951.1333611046695</v>
+        <v>951.1333611046697</v>
       </c>
       <c r="L91" s="131" t="n">
         <v>61.23579467953606</v>
@@ -19741,7 +19741,7 @@
         <v>21674.50215177691</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>991.3204392584844</v>
+        <v>991.3204392584845</v>
       </c>
       <c r="R91" s="131" t="n">
         <v>63.05746500463982</v>
@@ -19759,7 +19759,7 @@
         <v>1023.671300995067</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>64.74488708336855</v>
+        <v>64.74488708336854</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -19863,7 +19863,7 @@
         <v>3640.25820473868</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>961.92083159868</v>
+        <v>961.9208315986803</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>25.79473610836162</v>
@@ -19890,10 +19890,10 @@
         <v>16813.67286703419</v>
       </c>
       <c r="W93" s="131" t="n">
-        <v>4369.387256528761</v>
+        <v>4369.387256528762</v>
       </c>
       <c r="X93" s="131" t="n">
-        <v>1113.339510070846</v>
+        <v>1113.339510070845</v>
       </c>
       <c r="Y93" s="131" t="n">
         <v>27.25612941316352</v>
@@ -20000,10 +20000,10 @@
         <v>0</v>
       </c>
       <c r="M95" s="131" t="n">
-        <v>497.2321863036293</v>
+        <v>497.2321863036294</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>497.2321863036293</v>
+        <v>497.2321863036294</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>0</v>
@@ -20015,10 +20015,10 @@
         <v>0</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>531.6202297178928</v>
+        <v>531.6202297178926</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>531.6202297178928</v>
+        <v>531.6202297178926</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -20137,10 +20137,10 @@
         <v>22.80962481997878</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>3858.15130459552</v>
+        <v>3858.151304595521</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>3227.374752548553</v>
+        <v>3227.374752548552</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>689.3815929441711</v>
@@ -20152,22 +20152,22 @@
         <v>23.34018512080814</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>4189.016731019764</v>
+        <v>4189.016731019763</v>
       </c>
       <c r="V97" s="130" t="n">
         <v>3486.949013675067</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>748.9199100595179</v>
+        <v>748.9199100595183</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>267.5835762082338</v>
+        <v>267.5835762082337</v>
       </c>
       <c r="Y97" s="131" t="n">
         <v>24.13833300166812</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>4527.590832944486</v>
+        <v>4527.590832944487</v>
       </c>
     </row>
     <row r="98">
@@ -20268,7 +20268,7 @@
         <v>320.594759774991</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>16983.87938085577</v>
+        <v>16983.87938085576</v>
       </c>
       <c r="N99" s="132" t="n">
         <v>23292.7240438382</v>
@@ -20295,13 +20295,13 @@
         <v>1286.390850729047</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>409.1369923702005</v>
+        <v>409.1369923701932</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>20910.79825892893</v>
+        <v>20910.79825892892</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>29268.81067199288</v>
+        <v>29268.81067199286</v>
       </c>
     </row>
     <row r="100">
@@ -20350,10 +20350,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>18745.38435647285</v>
+        <v>18745.38435647284</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>18745.38435647285</v>
+        <v>18745.38435647284</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -20540,7 +20540,7 @@
         <v>57558.27330927954</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>413.0331345658013</v>
+        <v>413.0331345658014</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>1412872.598815222</v>
@@ -20555,7 +20555,7 @@
         <v>57902.36710961223</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>510.1782527668204</v>
+        <v>510.1782527668203</v>
       </c>
       <c r="T103" s="141" t="n">
         <v>1422103.938946906</v>
@@ -20634,10 +20634,10 @@
         <v>263015.0076298538</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>61298.40760621124</v>
+        <v>61298.40760621123</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>22180.09556515783</v>
+        <v>22180.09556515782</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>1550005.838670861</v>
@@ -21673,10 +21673,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>55719460.42474837</v>
+        <v>55719460.42474838</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>68660.92484379245</v>
+        <v>68660.92484379247</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -21692,7 +21692,7 @@
         </is>
       </c>
       <c r="AN25" s="48" t="n">
-        <v>673.04498458145</v>
+        <v>673.0449845814501</v>
       </c>
     </row>
     <row r="26">
@@ -21904,7 +21904,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>5310405.842538491</v>
+        <v>5310405.84253849</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>17641.43818058407</v>
@@ -22423,7 +22423,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>2029241.191294712</v>
+        <v>2029241.191294711</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>3570.123843302602</v>
@@ -23483,7 +23483,7 @@
         <v>3332.621486685727</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>833.0894434723068</v>
+        <v>833.0894434723069</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -23510,7 +23510,7 @@
         <v>6634.756448314753</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>3383.039931822101</v>
+        <v>3383.039931822102</v>
       </c>
       <c r="X53" s="128" t="n">
         <v>816.5124351978794</v>
@@ -23639,10 +23639,10 @@
         <v>20917</v>
       </c>
       <c r="J55" s="130" t="n">
-        <v>21080.77407711741</v>
+        <v>21080.77407711742</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>951.1333611046695</v>
+        <v>951.1333611046697</v>
       </c>
       <c r="L55" s="131" t="n">
         <v>61.23579467953606</v>
@@ -23657,7 +23657,7 @@
         <v>21674.50215177691</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>991.3204392584844</v>
+        <v>991.3204392584845</v>
       </c>
       <c r="R55" s="131" t="n">
         <v>63.05746500463982</v>
@@ -23675,7 +23675,7 @@
         <v>1023.671300995067</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>64.74488708336855</v>
+        <v>64.74488708336854</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -23801,19 +23801,19 @@
         <v>15485</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>6746.935336864784</v>
+        <v>6746.935336864786</v>
       </c>
       <c r="K57" s="131" t="n">
-        <v>1274.799268573767</v>
+        <v>1274.799268573766</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>468.5634983662505</v>
+        <v>468.5634983662507</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>10.76678424032055</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8501.064888045123</v>
+        <v>8501.064888045124</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>6890.578425007416</v>
@@ -23834,10 +23834,10 @@
         <v>7235.557701200762</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>1311.171925375474</v>
+        <v>1311.171925375475</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>478.4300451277439</v>
+        <v>478.4300451277438</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>11.62034978511225</v>
@@ -23972,10 +23972,10 @@
         <v>0</v>
       </c>
       <c r="M59" s="131" t="n">
-        <v>480.5890560334112</v>
+        <v>480.5890560334113</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>480.5890560334112</v>
+        <v>480.5890560334113</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>0</v>
@@ -23987,10 +23987,10 @@
         <v>0</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>503.5137707099607</v>
+        <v>503.5137707099605</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>503.5137707099607</v>
+        <v>503.5137707099605</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>0</v>
@@ -24019,7 +24019,7 @@
         <v>906466.490944769</v>
       </c>
       <c r="AH59" s="56" t="n">
-        <v>539.0692909435293</v>
+        <v>539.0692909435292</v>
       </c>
     </row>
     <row r="60">
@@ -24097,7 +24097,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>781605.0418458922</v>
+        <v>781605.0418458923</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>2348.723611867773</v>
@@ -24125,13 +24125,13 @@
         <v>27180</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>2379.655877793457</v>
+        <v>2379.655877793458</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>603.0630369926311</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>225.5148079810755</v>
+        <v>225.5148079810754</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>22.80962481997878</v>
@@ -24152,22 +24152,22 @@
         <v>23.34018512080814</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>3384.873682270296</v>
+        <v>3384.873682270295</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>2591.177460907065</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>671.6768219502637</v>
+        <v>671.6768219502641</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>247.0930019032081</v>
+        <v>247.093001903208</v>
       </c>
       <c r="Y61" s="131" t="n">
         <v>24.13833300166812</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>3534.085617762205</v>
+        <v>3534.085617762206</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -24293,7 +24293,7 @@
         <v>953.9922867363875</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>320.5947597749855</v>
+        <v>320.5947597749851</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>15681.27426545956</v>
@@ -24320,13 +24320,13 @@
         <v>6662.484569964501</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1286.390850729029</v>
+        <v>1286.390850729027</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>409.1369923701982</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>19269.94930292226</v>
+        <v>19269.94930292225</v>
       </c>
       <c r="Z63" s="132" t="n">
         <v>27627.96171598598</v>
@@ -24407,10 +24407,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>19197.57468923769</v>
+        <v>19197.57468923768</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>19197.57468923769</v>
+        <v>19197.57468923768</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -24623,16 +24623,16 @@
         <v>2662.427529471637</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>881.2611282689422</v>
+        <v>881.2611282689423</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>273.3095391711202</v>
+        <v>273.3095391711204</v>
       </c>
       <c r="N67" s="141" t="n">
         <v>14879.94587588111</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>8502.990848158244</v>
+        <v>8502.990848158246</v>
       </c>
       <c r="Q67" s="140" t="n">
         <v>1843.726306856785</v>
@@ -24641,7 +24641,7 @@
         <v>736.7815134418789</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>298.1160255987033</v>
+        <v>298.1160255987032</v>
       </c>
       <c r="T67" s="141" t="n">
         <v>11381.61469405561</v>
@@ -24653,7 +24653,7 @@
         <v>1343.153224553199</v>
       </c>
       <c r="X67" s="140" t="n">
-        <v>654.8099860584188</v>
+        <v>654.8099860584185</v>
       </c>
       <c r="Y67" s="140" t="n">
         <v>377.8047822787307</v>
@@ -24710,13 +24710,13 @@
         <v>16468.74926972439</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>97613.00453511404</v>
+        <v>97613.00453511406</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>51981.41011538231</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>9188.302808746161</v>
+        <v>9188.302808746163</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>2683.316339065291</v>
@@ -24725,7 +24725,7 @@
         <v>18174.27692598257</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>99296.33164210043</v>
+        <v>99296.33164210041</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>52470.61975794812</v>
@@ -24911,16 +24911,16 @@
         <v>6151.28413401941</v>
       </c>
       <c r="K71" s="128" t="n">
-        <v>1095.842816267823</v>
+        <v>1095.842816267824</v>
       </c>
       <c r="L71" s="128" t="n">
-        <v>353.777097941825</v>
+        <v>353.7770979418252</v>
       </c>
       <c r="M71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>7600.904048229057</v>
+        <v>7600.904048229059</v>
       </c>
       <c r="P71" s="127" t="n">
         <v>6287.041516213972</v>
@@ -24935,7 +24935,7 @@
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7785.634170715169</v>
+        <v>7785.634170715168</v>
       </c>
       <c r="V71" s="127" t="n">
         <v>6391.592060490513</v>
@@ -24944,7 +24944,7 @@
         <v>1169.252393113846</v>
       </c>
       <c r="X71" s="128" t="n">
-        <v>374.0976984907914</v>
+        <v>374.0976984907912</v>
       </c>
       <c r="Y71" s="128" t="n">
         <v>0</v>
@@ -25185,19 +25185,19 @@
         <v>493.3573332324296</v>
       </c>
       <c r="M75" s="131" t="n">
-        <v>15.02795186804108</v>
+        <v>15.02795186804107</v>
       </c>
       <c r="N75" s="132" t="n">
         <v>10741.10803940695</v>
       </c>
       <c r="P75" s="130" t="n">
-        <v>8778.963966004183</v>
+        <v>8778.963966004181</v>
       </c>
       <c r="Q75" s="131" t="n">
-        <v>2736.176993753839</v>
+        <v>2736.176993753838</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>571.1780149937247</v>
+        <v>571.1780149937246</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>15.32446357326684</v>
@@ -25212,7 +25212,7 @@
         <v>3058.215331153287</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>634.9094649431017</v>
+        <v>634.9094649431015</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>15.63577962805127</v>
@@ -25459,10 +25459,10 @@
         <v>627.1079570083781</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>740.6580467347986</v>
+        <v>740.6580467347984</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>50.76288255445774</v>
+        <v>50.76288255445775</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>12.72211946021124</v>
@@ -25471,22 +25471,22 @@
         <v>0</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>804.1430487494677</v>
+        <v>804.1430487494674</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>895.7715527680019</v>
+        <v>895.7715527680018</v>
       </c>
       <c r="W79" s="131" t="n">
-        <v>77.24308810925419</v>
+        <v>77.2430881092542</v>
       </c>
       <c r="X79" s="131" t="n">
-        <v>20.49057430502566</v>
+        <v>20.49057430502565</v>
       </c>
       <c r="Y79" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>993.5052151822819</v>
+        <v>993.5052151822817</v>
       </c>
     </row>
     <row r="80">
@@ -25587,10 +25587,10 @@
         <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>1302.605115396208</v>
+        <v>1302.605115396207</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>1302.605115396208</v>
+        <v>1302.605115396207</v>
       </c>
       <c r="P81" s="130" t="n">
         <v>0</v>
@@ -25614,13 +25614,13 @@
         <v>0</v>
       </c>
       <c r="X81" s="131" t="n">
-        <v>7.275957614183426e-12</v>
+        <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
         <v>1640.848956006674</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>1640.848956006681</v>
+        <v>1640.848956006674</v>
       </c>
     </row>
     <row r="82">
@@ -25654,10 +25654,10 @@
         <v>0</v>
       </c>
       <c r="M82" s="134" t="n">
-        <v>1302.605115396208</v>
+        <v>1302.605115396207</v>
       </c>
       <c r="N82" s="135" t="n">
-        <v>1302.605115396208</v>
+        <v>1302.605115396207</v>
       </c>
       <c r="P82" s="133" t="n">
         <v>0</v>
@@ -25889,7 +25889,7 @@
         <v>57598.1825207315</v>
       </c>
       <c r="Y85" s="140" t="n">
-        <v>267.2782745528123</v>
+        <v>267.2782745528122</v>
       </c>
       <c r="Z85" s="141" t="n">
         <v>1420894.459244691</v>
@@ -25953,7 +25953,7 @@
         <v>253995.9035744286</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>58627.68025847042</v>
+        <v>58627.68025847041</v>
       </c>
       <c r="Y86" s="143" t="n">
         <v>1977.290320302254</v>
@@ -26140,13 +26140,13 @@
         <v>0</v>
       </c>
       <c r="T89" s="129" t="n">
-        <v>18615.09985330715</v>
+        <v>18615.09985330716</v>
       </c>
       <c r="V89" s="127" t="n">
         <v>13026.34850880527</v>
       </c>
       <c r="W89" s="128" t="n">
-        <v>4552.292324935946</v>
+        <v>4552.292324935947</v>
       </c>
       <c r="X89" s="128" t="n">
         <v>1190.610133688671</v>
@@ -26247,10 +26247,10 @@
         <v>20917</v>
       </c>
       <c r="J91" s="130" t="n">
-        <v>21080.77407711741</v>
+        <v>21080.77407711742</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>951.1333611046695</v>
+        <v>951.1333611046697</v>
       </c>
       <c r="L91" s="131" t="n">
         <v>61.23579467953606</v>
@@ -26265,7 +26265,7 @@
         <v>21674.50215177691</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>991.3204392584844</v>
+        <v>991.3204392584845</v>
       </c>
       <c r="R91" s="131" t="n">
         <v>63.05746500463982</v>
@@ -26283,7 +26283,7 @@
         <v>1023.671300995067</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>64.74488708336855</v>
+        <v>64.74488708336854</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -26387,7 +26387,7 @@
         <v>3640.25820473868</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>961.92083159868</v>
+        <v>961.9208315986803</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>25.79473610836162</v>
@@ -26414,10 +26414,10 @@
         <v>16813.67286703419</v>
       </c>
       <c r="W93" s="131" t="n">
-        <v>4369.387256528761</v>
+        <v>4369.387256528762</v>
       </c>
       <c r="X93" s="131" t="n">
-        <v>1113.339510070846</v>
+        <v>1113.339510070845</v>
       </c>
       <c r="Y93" s="131" t="n">
         <v>27.25612941316352</v>
@@ -26524,10 +26524,10 @@
         <v>0</v>
       </c>
       <c r="M95" s="131" t="n">
-        <v>497.2321863036293</v>
+        <v>497.2321863036294</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>497.2321863036293</v>
+        <v>497.2321863036294</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>0</v>
@@ -26539,10 +26539,10 @@
         <v>0</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>531.6202297178928</v>
+        <v>531.6202297178926</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>531.6202297178928</v>
+        <v>531.6202297178926</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -26661,10 +26661,10 @@
         <v>22.80962481997878</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>3858.15130459552</v>
+        <v>3858.151304595521</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>3227.374752548553</v>
+        <v>3227.374752548552</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>689.3815929441711</v>
@@ -26676,22 +26676,22 @@
         <v>23.34018512080814</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>4189.016731019764</v>
+        <v>4189.016731019763</v>
       </c>
       <c r="V97" s="130" t="n">
         <v>3486.949013675067</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>748.9199100595179</v>
+        <v>748.9199100595183</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>267.5835762082338</v>
+        <v>267.5835762082337</v>
       </c>
       <c r="Y97" s="131" t="n">
         <v>24.13833300166812</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>4527.590832944486</v>
+        <v>4527.590832944487</v>
       </c>
     </row>
     <row r="98">
@@ -26792,7 +26792,7 @@
         <v>320.594759774991</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>16983.87938085577</v>
+        <v>16983.87938085576</v>
       </c>
       <c r="N99" s="132" t="n">
         <v>23292.7240438382</v>
@@ -26819,13 +26819,13 @@
         <v>1286.390850729047</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>409.1369923702005</v>
+        <v>409.1369923701932</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>20910.79825892893</v>
+        <v>20910.79825892892</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>29268.81067199288</v>
+        <v>29268.81067199286</v>
       </c>
     </row>
     <row r="100">
@@ -26874,10 +26874,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>18745.38435647285</v>
+        <v>18745.38435647284</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>18745.38435647285</v>
+        <v>18745.38435647284</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -27064,7 +27064,7 @@
         <v>57558.27330927954</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>413.0331345658013</v>
+        <v>413.0331345658014</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>1412872.598815222</v>
@@ -27079,7 +27079,7 @@
         <v>57902.36710961223</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>510.1782527668204</v>
+        <v>510.1782527668203</v>
       </c>
       <c r="T103" s="141" t="n">
         <v>1422103.938946906</v>
@@ -27158,10 +27158,10 @@
         <v>263015.0076298538</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>61298.40760621124</v>
+        <v>61298.40760621123</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>22180.09556515783</v>
+        <v>22180.09556515782</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>1550005.838670861</v>
@@ -28197,7 +28197,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>69285584.18914481</v>
+        <v>69285584.18914482</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>82393.1061648711</v>
@@ -28293,7 +28293,7 @@
         </is>
       </c>
       <c r="AN26" s="58" t="n">
-        <v>418.9450962243397</v>
+        <v>418.9450962243398</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" thickBot="1">
@@ -28428,7 +28428,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>6109904.890164006</v>
+        <v>6109904.890164007</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>19791.41132971137</v>
@@ -28947,7 +28947,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>2261110.921757243</v>
+        <v>2261110.921757242</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>2957.226786839574</v>
@@ -29101,10 +29101,10 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>1704572.018423963</v>
+        <v>1704572.018423962</v>
       </c>
       <c r="AI37" s="56" t="n">
-        <v>1964.648020269052</v>
+        <v>1964.648020269053</v>
       </c>
       <c r="AK37" s="123" t="n">
         <v>13</v>
@@ -29178,10 +29178,10 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>1628208.049291218</v>
+        <v>1628208.049291219</v>
       </c>
       <c r="AI38" s="56" t="n">
-        <v>2218.827294049512</v>
+        <v>2218.827294049513</v>
       </c>
       <c r="AK38" s="123" t="n">
         <v>14</v>
@@ -29308,10 +29308,10 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>1451451.325188484</v>
+        <v>1451451.325188483</v>
       </c>
       <c r="AI40" s="56" t="n">
-        <v>2609.805879037139</v>
+        <v>2609.80587903714</v>
       </c>
       <c r="AK40" s="123" t="n">
         <v>16</v>
@@ -29539,10 +29539,10 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>1120636.867675033</v>
+        <v>1120636.867675034</v>
       </c>
       <c r="AI43" s="56" t="n">
-        <v>841.3274271956741</v>
+        <v>841.3274271956742</v>
       </c>
       <c r="AK43" s="123" t="n">
         <v>19</v>
@@ -29619,7 +29619,7 @@
         <v>936392.4561784337</v>
       </c>
       <c r="AI44" s="84" t="n">
-        <v>176.4354214434484</v>
+        <v>176.4354214434485</v>
       </c>
       <c r="AK44" s="126" t="n">
         <v>20</v>
@@ -30007,7 +30007,7 @@
         <v>3332.621486685727</v>
       </c>
       <c r="L53" s="128" t="n">
-        <v>833.0894434723068</v>
+        <v>833.0894434723069</v>
       </c>
       <c r="M53" s="128" t="n">
         <v>0</v>
@@ -30034,7 +30034,7 @@
         <v>6634.756448314753</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>3383.039931822101</v>
+        <v>3383.039931822102</v>
       </c>
       <c r="X53" s="128" t="n">
         <v>816.5124351978794</v>
@@ -30163,10 +30163,10 @@
         <v>20917</v>
       </c>
       <c r="J55" s="130" t="n">
-        <v>21080.77407711741</v>
+        <v>21080.77407711742</v>
       </c>
       <c r="K55" s="131" t="n">
-        <v>951.1333611046695</v>
+        <v>951.1333611046697</v>
       </c>
       <c r="L55" s="131" t="n">
         <v>61.23579467953606</v>
@@ -30181,7 +30181,7 @@
         <v>21674.50215177691</v>
       </c>
       <c r="Q55" s="131" t="n">
-        <v>991.3204392584844</v>
+        <v>991.3204392584845</v>
       </c>
       <c r="R55" s="131" t="n">
         <v>63.05746500463982</v>
@@ -30199,7 +30199,7 @@
         <v>1023.671300995067</v>
       </c>
       <c r="X55" s="131" t="n">
-        <v>64.74488708336855</v>
+        <v>64.74488708336854</v>
       </c>
       <c r="Y55" s="131" t="n">
         <v>0</v>
@@ -30325,19 +30325,19 @@
         <v>15485</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>6746.935336864784</v>
+        <v>6746.935336864786</v>
       </c>
       <c r="K57" s="131" t="n">
-        <v>1274.799268573767</v>
+        <v>1274.799268573766</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>468.5634983662505</v>
+        <v>468.5634983662507</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>10.76678424032055</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8501.064888045123</v>
+        <v>8501.064888045124</v>
       </c>
       <c r="P57" s="130" t="n">
         <v>6890.578425007416</v>
@@ -30358,10 +30358,10 @@
         <v>7235.557701200762</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>1311.171925375474</v>
+        <v>1311.171925375475</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>478.4300451277439</v>
+        <v>478.4300451277438</v>
       </c>
       <c r="Y57" s="131" t="n">
         <v>11.62034978511225</v>
@@ -30496,10 +30496,10 @@
         <v>0</v>
       </c>
       <c r="M59" s="131" t="n">
-        <v>480.5890560334112</v>
+        <v>480.5890560334113</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>480.5890560334112</v>
+        <v>480.5890560334113</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>0</v>
@@ -30511,10 +30511,10 @@
         <v>0</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>503.5137707099607</v>
+        <v>503.5137707099605</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>503.5137707099607</v>
+        <v>503.5137707099605</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>0</v>
@@ -30649,13 +30649,13 @@
         <v>27180</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>2379.655877793457</v>
+        <v>2379.655877793458</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>603.0630369926311</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>225.5148079810755</v>
+        <v>225.5148079810754</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>22.80962481997878</v>
@@ -30676,22 +30676,22 @@
         <v>23.34018512080814</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>3384.873682270296</v>
+        <v>3384.873682270295</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>2591.177460907065</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>671.6768219502637</v>
+        <v>671.6768219502641</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>247.0930019032081</v>
+        <v>247.093001903208</v>
       </c>
       <c r="Y61" s="131" t="n">
         <v>24.13833300166812</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>3534.085617762205</v>
+        <v>3534.085617762206</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -30817,7 +30817,7 @@
         <v>953.9922867363875</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>320.5947597749855</v>
+        <v>320.5947597749851</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>15681.27426545956</v>
@@ -30844,13 +30844,13 @@
         <v>6662.484569964501</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>1286.390850729029</v>
+        <v>1286.390850729027</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>409.1369923701982</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>19269.94930292226</v>
+        <v>19269.94930292225</v>
       </c>
       <c r="Z63" s="132" t="n">
         <v>27627.96171598598</v>
@@ -30931,10 +30931,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>19197.57468923769</v>
+        <v>19197.57468923768</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>19197.57468923769</v>
+        <v>19197.57468923768</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -31116,7 +31116,7 @@
         <v>187191.9019934708</v>
       </c>
       <c r="AH66" s="56" t="n">
-        <v>346.6790497903376</v>
+        <v>346.6790497903377</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" thickBot="1">
@@ -31147,16 +31147,16 @@
         <v>2662.427529471637</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>881.2611282689422</v>
+        <v>881.2611282689423</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>273.3095391711202</v>
+        <v>273.3095391711204</v>
       </c>
       <c r="N67" s="141" t="n">
         <v>14879.94587588111</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>8502.990848158244</v>
+        <v>8502.990848158246</v>
       </c>
       <c r="Q67" s="140" t="n">
         <v>1843.726306856785</v>
@@ -31165,7 +31165,7 @@
         <v>736.7815134418789</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>298.1160255987033</v>
+        <v>298.1160255987032</v>
       </c>
       <c r="T67" s="141" t="n">
         <v>11381.61469405561</v>
@@ -31177,7 +31177,7 @@
         <v>1343.153224553199</v>
       </c>
       <c r="X67" s="140" t="n">
-        <v>654.8099860584188</v>
+        <v>654.8099860584185</v>
       </c>
       <c r="Y67" s="140" t="n">
         <v>377.8047822787307</v>
@@ -31197,7 +31197,7 @@
         <v>174547.3892622732</v>
       </c>
       <c r="AH67" s="56" t="n">
-        <v>662.7618445907182</v>
+        <v>662.7618445907183</v>
       </c>
     </row>
     <row r="68" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -31234,13 +31234,13 @@
         <v>16468.74926972439</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>97613.00453511404</v>
+        <v>97613.00453511406</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>51981.41011538231</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>9188.302808746161</v>
+        <v>9188.302808746163</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>2683.316339065291</v>
@@ -31249,7 +31249,7 @@
         <v>18174.27692598257</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>99296.33164210043</v>
+        <v>99296.33164210041</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>52470.61975794812</v>
@@ -31435,16 +31435,16 @@
         <v>6151.28413401941</v>
       </c>
       <c r="K71" s="128" t="n">
-        <v>1095.842816267823</v>
+        <v>1095.842816267824</v>
       </c>
       <c r="L71" s="128" t="n">
-        <v>353.777097941825</v>
+        <v>353.7770979418252</v>
       </c>
       <c r="M71" s="128" t="n">
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>7600.904048229057</v>
+        <v>7600.904048229059</v>
       </c>
       <c r="P71" s="127" t="n">
         <v>6287.041516213972</v>
@@ -31459,7 +31459,7 @@
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7785.634170715169</v>
+        <v>7785.634170715168</v>
       </c>
       <c r="V71" s="127" t="n">
         <v>6391.592060490513</v>
@@ -31468,7 +31468,7 @@
         <v>1169.252393113846</v>
       </c>
       <c r="X71" s="128" t="n">
-        <v>374.0976984907914</v>
+        <v>374.0976984907912</v>
       </c>
       <c r="Y71" s="128" t="n">
         <v>0</v>
@@ -31709,19 +31709,19 @@
         <v>493.3573332324296</v>
       </c>
       <c r="M75" s="131" t="n">
-        <v>15.02795186804108</v>
+        <v>15.02795186804107</v>
       </c>
       <c r="N75" s="132" t="n">
         <v>10741.10803940695</v>
       </c>
       <c r="P75" s="130" t="n">
-        <v>8778.963966004183</v>
+        <v>8778.963966004181</v>
       </c>
       <c r="Q75" s="131" t="n">
-        <v>2736.176993753839</v>
+        <v>2736.176993753838</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>571.1780149937247</v>
+        <v>571.1780149937246</v>
       </c>
       <c r="S75" s="131" t="n">
         <v>15.32446357326684</v>
@@ -31736,7 +31736,7 @@
         <v>3058.215331153287</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>634.9094649431017</v>
+        <v>634.9094649431015</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>15.63577962805127</v>
@@ -31983,10 +31983,10 @@
         <v>627.1079570083781</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>740.6580467347986</v>
+        <v>740.6580467347984</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>50.76288255445774</v>
+        <v>50.76288255445775</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>12.72211946021124</v>
@@ -31995,22 +31995,22 @@
         <v>0</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>804.1430487494677</v>
+        <v>804.1430487494674</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>895.7715527680019</v>
+        <v>895.7715527680018</v>
       </c>
       <c r="W79" s="131" t="n">
-        <v>77.24308810925419</v>
+        <v>77.2430881092542</v>
       </c>
       <c r="X79" s="131" t="n">
-        <v>20.49057430502566</v>
+        <v>20.49057430502565</v>
       </c>
       <c r="Y79" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>993.5052151822819</v>
+        <v>993.5052151822817</v>
       </c>
     </row>
     <row r="80">
@@ -32111,10 +32111,10 @@
         <v>0</v>
       </c>
       <c r="M81" s="131" t="n">
-        <v>1302.605115396208</v>
+        <v>1302.605115396207</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>1302.605115396208</v>
+        <v>1302.605115396207</v>
       </c>
       <c r="P81" s="130" t="n">
         <v>0</v>
@@ -32138,13 +32138,13 @@
         <v>0</v>
       </c>
       <c r="X81" s="131" t="n">
-        <v>7.275957614183426e-12</v>
+        <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
         <v>1640.848956006674</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>1640.848956006681</v>
+        <v>1640.848956006674</v>
       </c>
     </row>
     <row r="82">
@@ -32178,10 +32178,10 @@
         <v>0</v>
       </c>
       <c r="M82" s="134" t="n">
-        <v>1302.605115396208</v>
+        <v>1302.605115396207</v>
       </c>
       <c r="N82" s="135" t="n">
-        <v>1302.605115396208</v>
+        <v>1302.605115396207</v>
       </c>
       <c r="P82" s="133" t="n">
         <v>0</v>
@@ -32413,7 +32413,7 @@
         <v>57598.1825207315</v>
       </c>
       <c r="Y85" s="140" t="n">
-        <v>267.2782745528123</v>
+        <v>267.2782745528122</v>
       </c>
       <c r="Z85" s="141" t="n">
         <v>1420894.459244691</v>
@@ -32477,7 +32477,7 @@
         <v>253995.9035744286</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>58627.68025847042</v>
+        <v>58627.68025847041</v>
       </c>
       <c r="Y86" s="143" t="n">
         <v>1977.290320302254</v>
@@ -32664,13 +32664,13 @@
         <v>0</v>
       </c>
       <c r="T89" s="129" t="n">
-        <v>18615.09985330715</v>
+        <v>18615.09985330716</v>
       </c>
       <c r="V89" s="127" t="n">
         <v>13026.34850880527</v>
       </c>
       <c r="W89" s="128" t="n">
-        <v>4552.292324935946</v>
+        <v>4552.292324935947</v>
       </c>
       <c r="X89" s="128" t="n">
         <v>1190.610133688671</v>
@@ -32771,10 +32771,10 @@
         <v>20917</v>
       </c>
       <c r="J91" s="130" t="n">
-        <v>21080.77407711741</v>
+        <v>21080.77407711742</v>
       </c>
       <c r="K91" s="131" t="n">
-        <v>951.1333611046695</v>
+        <v>951.1333611046697</v>
       </c>
       <c r="L91" s="131" t="n">
         <v>61.23579467953606</v>
@@ -32789,7 +32789,7 @@
         <v>21674.50215177691</v>
       </c>
       <c r="Q91" s="131" t="n">
-        <v>991.3204392584844</v>
+        <v>991.3204392584845</v>
       </c>
       <c r="R91" s="131" t="n">
         <v>63.05746500463982</v>
@@ -32807,7 +32807,7 @@
         <v>1023.671300995067</v>
       </c>
       <c r="X91" s="131" t="n">
-        <v>64.74488708336855</v>
+        <v>64.74488708336854</v>
       </c>
       <c r="Y91" s="131" t="n">
         <v>0</v>
@@ -32911,7 +32911,7 @@
         <v>3640.25820473868</v>
       </c>
       <c r="L93" s="131" t="n">
-        <v>961.92083159868</v>
+        <v>961.9208315986803</v>
       </c>
       <c r="M93" s="131" t="n">
         <v>25.79473610836162</v>
@@ -32938,10 +32938,10 @@
         <v>16813.67286703419</v>
       </c>
       <c r="W93" s="131" t="n">
-        <v>4369.387256528761</v>
+        <v>4369.387256528762</v>
       </c>
       <c r="X93" s="131" t="n">
-        <v>1113.339510070846</v>
+        <v>1113.339510070845</v>
       </c>
       <c r="Y93" s="131" t="n">
         <v>27.25612941316352</v>
@@ -33048,10 +33048,10 @@
         <v>0</v>
       </c>
       <c r="M95" s="131" t="n">
-        <v>497.2321863036293</v>
+        <v>497.2321863036294</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>497.2321863036293</v>
+        <v>497.2321863036294</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>0</v>
@@ -33063,10 +33063,10 @@
         <v>0</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>531.6202297178928</v>
+        <v>531.6202297178926</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>531.6202297178928</v>
+        <v>531.6202297178926</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -33185,10 +33185,10 @@
         <v>22.80962481997878</v>
       </c>
       <c r="N97" s="132" t="n">
-        <v>3858.15130459552</v>
+        <v>3858.151304595521</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>3227.374752548553</v>
+        <v>3227.374752548552</v>
       </c>
       <c r="Q97" s="131" t="n">
         <v>689.3815929441711</v>
@@ -33200,22 +33200,22 @@
         <v>23.34018512080814</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>4189.016731019764</v>
+        <v>4189.016731019763</v>
       </c>
       <c r="V97" s="130" t="n">
         <v>3486.949013675067</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>748.9199100595179</v>
+        <v>748.9199100595183</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>267.5835762082338</v>
+        <v>267.5835762082337</v>
       </c>
       <c r="Y97" s="131" t="n">
         <v>24.13833300166812</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>4527.590832944486</v>
+        <v>4527.590832944487</v>
       </c>
     </row>
     <row r="98">
@@ -33316,7 +33316,7 @@
         <v>320.594759774991</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>16983.87938085577</v>
+        <v>16983.87938085576</v>
       </c>
       <c r="N99" s="132" t="n">
         <v>23292.7240438382</v>
@@ -33343,13 +33343,13 @@
         <v>1286.390850729047</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>409.1369923702005</v>
+        <v>409.1369923701932</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>20910.79825892893</v>
+        <v>20910.79825892892</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>29268.81067199288</v>
+        <v>29268.81067199286</v>
       </c>
     </row>
     <row r="100">
@@ -33398,10 +33398,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>18745.38435647285</v>
+        <v>18745.38435647284</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>18745.38435647285</v>
+        <v>18745.38435647284</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -33588,7 +33588,7 @@
         <v>57558.27330927954</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>413.0331345658013</v>
+        <v>413.0331345658014</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>1412872.598815222</v>
@@ -33603,7 +33603,7 @@
         <v>57902.36710961223</v>
       </c>
       <c r="S103" s="140" t="n">
-        <v>510.1782527668204</v>
+        <v>510.1782527668203</v>
       </c>
       <c r="T103" s="141" t="n">
         <v>1422103.938946906</v>
@@ -33682,10 +33682,10 @@
         <v>263015.0076298538</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>61298.40760621124</v>
+        <v>61298.40760621123</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>22180.09556515783</v>
+        <v>22180.09556515782</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>1550005.838670861</v>
